--- a/data/archive/golden/zone_rollup.xlsx
+++ b/data/archive/golden/zone_rollup.xlsx
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>추진위 승인</t>
+          <t>조합설립인가</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
